--- a/sesame_chicken.xlsx
+++ b/sesame_chicken.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centralesupelec-my.sharepoint.com/personal/benjamin_dieu2_student-cs_fr/Documents/EXTRA/HEALTH_FITNESS/Recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{74DCF865-7CC1-3F4E-A6B4-5C6A1802CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FF26BD-9C4C-F044-9EAD-FE6577112CDF}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{74DCF865-7CC1-3F4E-A6B4-5C6A1802CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13FEA2B4-F73A-B14A-B7E0-104FE7755436}"/>
   <bookViews>
     <workbookView xWindow="15580" yWindow="660" windowWidth="13820" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Servings (base)</t>
   </si>
@@ -56,60 +56,18 @@
     <t xml:space="preserve">Chicken </t>
   </si>
   <si>
-    <t>ml</t>
-  </si>
-  <si>
-    <t>Honey</t>
-  </si>
-  <si>
     <t>Sesame chicken</t>
   </si>
   <si>
-    <t>Eggs</t>
-  </si>
-  <si>
-    <t>units</t>
-  </si>
-  <si>
-    <t>All-purpose flour</t>
-  </si>
-  <si>
     <t>Cornstarch</t>
   </si>
   <si>
-    <t>Frying oil</t>
-  </si>
-  <si>
-    <t>Vegetable oil</t>
-  </si>
-  <si>
-    <t>teaspoon</t>
-  </si>
-  <si>
-    <t>Garlic</t>
-  </si>
-  <si>
-    <t>clove</t>
-  </si>
-  <si>
     <t>tablespoons</t>
   </si>
   <si>
-    <t>Soy Sauce</t>
-  </si>
-  <si>
     <t>Ketchup</t>
   </si>
   <si>
-    <t>Sugar</t>
-  </si>
-  <si>
-    <t>Rice Vinegar</t>
-  </si>
-  <si>
-    <t>Sesame oil</t>
-  </si>
-  <si>
     <t>Sesame seeds</t>
   </si>
   <si>
@@ -117,6 +75,33 @@
   </si>
   <si>
     <t>https://www.dinneratthezoo.com/lighter-honey-sesame-chicken/</t>
+  </si>
+  <si>
+    <t>Place the eggs, salt and pepper in a bowl. Stir to combine</t>
+  </si>
+  <si>
+    <t>Place the flour and 1/2 cup of cornstarch in a shallow bowl or on a plate. Stir to combine.</t>
+  </si>
+  <si>
+    <t>Dip each piece of chicken into the egg mixture, then into the flour. Repeat the process with all of the chicken.</t>
+  </si>
+  <si>
+    <t>Heat 3 inches of oil in a deep pan to 350 degrees F</t>
+  </si>
+  <si>
+    <t>Add 7-8 pieces of chicken to the pan. Cook for 5 minutes or until crispy and golden brown. Repeat the process with the remaining chicken</t>
+  </si>
+  <si>
+    <t>Drain the chicken on paper towels</t>
+  </si>
+  <si>
+    <t>While the chicken is cooking, combine the honey, soy sauce, ketchup, brown sugar, rice vinegar, sesame oil and 2 teaspoons of cornstarch in a bowl.</t>
+  </si>
+  <si>
+    <t>Heat the teaspoon of oil in a large pan over medium heat. Add the garlic and cook for 30 seconds. Add the honey sauce mixture and bring to a simmer. Cook for 3-4 minutes or until just thickened.</t>
+  </si>
+  <si>
+    <t>Add the crispy chicken to the pan and toss to coat with the sauce. Sprinkle with sesame seeds and green onions, then serve.</t>
   </si>
 </sst>
 </file>
@@ -126,7 +111,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +152,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0D2E51"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -237,7 +228,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -258,22 +249,15 @@
     <xf numFmtId="43" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -578,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -587,11 +571,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="A1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -601,8 +585,8 @@
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="17" t="s">
-        <v>27</v>
+      <c r="D2" s="11" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -630,7 +614,7 @@
       <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
@@ -642,186 +626,91 @@
       <c r="C5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="9">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="9">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="5">
+        <f>70/4</f>
+        <v>17.5</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="14" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="7">
-        <v>15</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="14"/>
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5">
+        <f>2/4</f>
+        <v>0.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5">
-        <f>70/4</f>
-        <v>17.5</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="5">
         <f>2/4</f>
         <v>0.5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E10" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="14"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="5">
-        <f>2/4</f>
-        <v>0.5</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="5">
-        <f>1/4</f>
-        <v>0.25</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="14" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="5">
-        <f>2/4</f>
-        <v>0.5</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="14" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="7">
-        <f>50/4</f>
-        <v>12.5</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="11">
-        <f>1/4</f>
-        <v>0.25</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="11">
-        <f>1/4</f>
-        <v>0.25</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="11">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="E14" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="11">
-        <f>2/4</f>
-        <v>0.5</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
